--- a/job_details.xlsx
+++ b/job_details.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="65">
   <si>
     <t>serial number</t>
   </si>
@@ -94,12 +94,6 @@
   </si>
   <si>
     <t>sohan sharma</t>
-  </si>
-  <si>
-    <t>22/09/2025</t>
-  </si>
-  <si>
-    <t>27/09/2025</t>
   </si>
   <si>
     <t>tksr</t>
@@ -148,16 +142,10 @@
     <t>Company Name</t>
   </si>
   <si>
-    <t>27/09/2026</t>
-  </si>
-  <si>
     <t>prathmeshvaidya20@tskr.com</t>
   </si>
   <si>
     <t>prathmeshvaidya20@tksr.com</t>
-  </si>
-  <si>
-    <t>30/09/2025</t>
   </si>
   <si>
     <t xml:space="preserve">Job description
@@ -202,15 +190,98 @@
   <si>
     <t>vaidyaprathmesh20@gmail.com</t>
   </si>
+  <si>
+    <t>tksr.user@gmail.com</t>
+  </si>
+  <si>
+    <t>testing) to ensure successful and timely completion of projects
+Provide guidance and support to team members in creating comprehensive project implementation plans
+Work closely with a development team to accurately interpret and implement business requirements
+What youll bring:
+Bachelor's or Master's degree in Business Analytics, Computer Science, MIS or related field with academic excellence
+Proficiency in RDBMS concepts, SQL, and programming languages such as Python
+Strong analytical and problem-solving skills to convert intricate business requirements into technology solutions
+Knowledge of algorithms and data structures
+Additional Skills:
+0-3+ years of relevant professional experience in delivering small/medium-scale technology solutions
+Strong verbal and written communication skills to effectively convey results and issues to internal and client teams Familiarity with Big Data Concepts and Cloud Platforms like AWS, Azure, and Google Cloud Platform
+Understanding of productivity tools such as co-pilot and SQL generation</t>
+  </si>
+  <si>
+    <t>tksr user</t>
+  </si>
+  <si>
+    <t>user</t>
+  </si>
+  <si>
+    <t>30/09/2025 00:00:00</t>
+  </si>
+  <si>
+    <t>ZS Associates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bachelor's or Master's degree in Business Analytics, Computer </t>
+  </si>
+  <si>
+    <t>Prathmesh Vaidya</t>
+  </si>
+  <si>
+    <t>TechNova Solutions</t>
+  </si>
+  <si>
+    <t>Senior Data Scientist role. Requires 5+ years experience in Big Data, AWS, and Machine Learning model deployment. Strong communication skills and experience leading small teams.</t>
+  </si>
+  <si>
+    <t>Sarah Connor</t>
+  </si>
+  <si>
+    <t>sarah.connor@technovasolutions.com</t>
+  </si>
+  <si>
+    <t>Global Innovations Inc.</t>
+  </si>
+  <si>
+    <t>Lead Python Developer position. Must have expertise in Django, Flask, and REST API development. Familiarity with Agile methodologies and CI/CD pipelines is a must.</t>
+  </si>
+  <si>
+    <t>Alpha Consulting Group</t>
+  </si>
+  <si>
+    <t>Junior Business Analyst. 0-2 years experience. Must have proficiency in MS Excel and report generation. SQL knowledge is a plus.</t>
+  </si>
+  <si>
+    <t>Analyze data, apply statistical methods, and generate regular reports [6].
+Establish and execute data management systems, incorporating analytics for optimal statistical performance [6].</t>
+  </si>
+  <si>
+    <t>Impact HR &amp; KM Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experience in building ML models in cloud environments (At least 1 of the 3: Azure ML, GCP’s Vertex AI platform, AWS SageMaker) 
+Knowledge of predictive/prescriptive analytics, especially on usage of Log-Log, Log-Linear, Bayesian Regression technques and including Machine Learning algorithms (Supervised and Unsupervised) and deep learning algorithms and Artificial Neural Networks 
+Good knowledge of statistics For e.g: statistical tests &amp; distributions </t>
+  </si>
+  <si>
+    <t>What would you do? DATA &amp; AI An interdisciplinary field about scientific methods, processes and systems to extract knowledge or insights from data in various forms, either structured or unstructured.</t>
+  </si>
+  <si>
+    <t>accenture</t>
+  </si>
+  <si>
+    <t>`PwC US - Acceleration Center</t>
+  </si>
+  <si>
+    <t>pooja</t>
+  </si>
+  <si>
+    <t>amit</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
-  </numFmts>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -238,6 +309,19 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9E9E9E"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -276,18 +360,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -593,7 +680,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.28515625" bestFit="1" customWidth="1"/>
@@ -612,7 +699,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -628,7 +715,7 @@
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="8">
         <v>45901</v>
       </c>
       <c r="C2" t="s">
@@ -648,7 +735,7 @@
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="8">
         <v>45902</v>
       </c>
       <c r="C3" t="s">
@@ -668,7 +755,7 @@
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="8">
         <v>45903</v>
       </c>
       <c r="C4" t="s">
@@ -685,7 +772,7 @@
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="8">
         <v>45904</v>
       </c>
       <c r="C5" t="s">
@@ -705,7 +792,7 @@
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="8">
         <v>45905</v>
       </c>
       <c r="C6" t="s">
@@ -722,14 +809,14 @@
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" s="4" t="s">
+      <c r="B7" s="8">
+        <v>45906</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>28</v>
+      <c r="D7" s="2" t="s">
+        <v>26</v>
       </c>
       <c r="E7" t="s">
         <v>24</v>
@@ -739,97 +826,273 @@
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
-        <v>26</v>
+      <c r="B8" s="8">
+        <v>45907</v>
       </c>
       <c r="C8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>29</v>
-      </c>
       <c r="E8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F8" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="90" customHeight="1">
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
-        <v>34</v>
+      <c r="B9" s="8">
+        <v>45908</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>31</v>
+        <v>25</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="E9" t="s">
+        <v>30</v>
+      </c>
+      <c r="F9" t="s">
         <v>32</v>
-      </c>
-      <c r="F9" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="144.75" customHeight="1">
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" t="s">
-        <v>37</v>
+      <c r="B10" s="8">
+        <v>45909</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>38</v>
+        <v>35</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="E10" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="105">
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="8">
+        <v>45910</v>
+      </c>
+      <c r="C11" t="s">
         <v>37</v>
       </c>
-      <c r="C11" t="s">
-        <v>41</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>42</v>
+      <c r="D11" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="E11" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F11" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="105">
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="8">
+        <v>45911</v>
+      </c>
+      <c r="C12" t="s">
         <v>37</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E12" t="s">
+        <v>30</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="351" customHeight="1">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" s="8">
+        <v>45912</v>
+      </c>
+      <c r="C13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E13" t="s">
+        <v>43</v>
+      </c>
+      <c r="F13" t="s">
         <v>41</v>
       </c>
-      <c r="D12" s="3" t="s">
+    </row>
+    <row r="14" spans="1:6" ht="315">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" s="8">
+        <v>45913</v>
+      </c>
+      <c r="C14" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E12" t="s">
-        <v>32</v>
-      </c>
-      <c r="F12" s="6" t="s">
+      <c r="E14" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="315">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" s="8">
+        <v>45726</v>
+      </c>
+      <c r="C15" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E15" t="s">
         <v>44</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" t="s">
+        <v>47</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" s="9">
+        <v>45726</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" s="9">
+        <v>45726</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F18" s="6"/>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" s="9">
+        <v>45757</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+    </row>
+    <row r="20" spans="1:6" ht="39.75" customHeight="1">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" s="9">
+        <v>45757</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="105">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" s="9">
+        <v>45757</v>
+      </c>
+      <c r="C21" t="s">
+        <v>62</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" s="9">
+        <v>45757</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -837,5 +1100,6 @@
     <hyperlink ref="F12" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>